--- a/product_selector_out/STM32H743-753.xlsx
+++ b/product_selector_out/STM32H743-753.xlsx
@@ -13856,7 +13856,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14450,7 +14450,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14516,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14846,7 +14846,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 13. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the footnote qualifies the figure</t>
+          <t>Table 14. General operating conditions: V_DD min reads '1.62(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32H743-753.xlsx
+++ b/product_selector_out/STM32H743-753.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO29"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.79296875" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -4034,6 +4081,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -4371,6 +4423,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -4708,6 +4765,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -5045,6 +5107,11 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -5382,6 +5449,11 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -5719,6 +5791,11 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -6056,6 +6133,11 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -6393,6 +6475,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
@@ -6730,6 +6817,11 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h753ai.pdf</t>
         </is>
       </c>
@@ -7067,12 +7159,17 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h742ag.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -7095,12 +7192,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -7115,9 +7214,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -7171,7 +7269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO29"/>
+  <dimension ref="A1:BP29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7241,6 +7339,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7584,6 +7683,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -7681,6 +7785,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -8013,7 +8118,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8350,7 +8460,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8687,7 +8802,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9024,7 +9144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9361,7 +9486,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9698,7 +9828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10035,7 +10170,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10372,7 +10512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10709,7 +10854,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11046,7 +11196,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11383,7 +11538,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11720,7 +11880,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12057,7 +12222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12394,7 +12564,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12731,7 +12906,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13068,7 +13248,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13405,7 +13590,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13742,7 +13932,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13750,8 +13945,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
